--- a/etf_holdings/2026-10-20_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00400A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:33</t>
+          <t>2026-10-20 21:45:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2420</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.71%1,094,000</t>
+          <t>9.11%1,131,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.71%</t>
+          <t>9.11%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1094000</v>
+        <v>1131000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:33</t>
+          <t>2026-10-20 21:45:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,33 +570,33 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.06%4205</t>
+          <t>-1.31%4150</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4205</v>
+        <v>4150</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.16%445,000</t>
+          <t>7.15%514,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>7.15%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>445000</v>
+        <v>514000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:33</t>
+          <t>2026-10-20 21:45:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.77%5125</t>
+          <t>-3.51%4945</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5125</v>
+        <v>4945</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.28%254,000</t>
+          <t>4.21%254,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.28%</t>
+          <t>4.21%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:33</t>
+          <t>2026-10-20 21:45:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-1.14%303.5</t>
+          <t>-2.47%296</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-2.47%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>303.5</v>
+        <v>296</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.16%4,167,000</t>
+          <t>4.13%4,167,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.16%</t>
+          <t>4.13%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:33</t>
+          <t>2026-10-20 21:45:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.75%1120</t>
+          <t>+1.81%10100</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.75%</t>
+          <t>+1.81%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1120</v>
+        <v>10100</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.94%1,069,000</t>
+          <t>3.79%112,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>3.79%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1069000</v>
+        <v>112000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:33</t>
+          <t>2026-10-20 21:45:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.15%3320</t>
+          <t>-5.8%1055</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3320</v>
+        <v>1055</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.59%329,000</t>
+          <t>3.78%1,069,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.78%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>329000</v>
+        <v>1069000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:33</t>
+          <t>2026-10-20 21:45:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.53%6560</t>
+          <t>+0.15%3325</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6560</v>
+        <v>3325</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.32%154,000</t>
+          <t>3.67%329,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>154000</v>
+        <v>329000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:33</t>
+          <t>2026-10-20 21:45:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.58%5235</t>
+          <t>+1.37%6650</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5235</v>
+        <v>6650</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.12%181,000</t>
+          <t>3.43%154,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>181000</v>
+        <v>154000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:33</t>
+          <t>2026-10-20 21:45:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.25%2005</t>
+          <t>-0.25%2000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2005</v>
+        <v>2000</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.10%470,000</t>
+          <t>3.15%470,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:33</t>
+          <t>2026-10-20 21:45:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.4%1250</t>
+          <t>-6.4%4900</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1250</v>
+        <v>4900</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.02%734,000</t>
+          <t>2.97%181,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>2.97%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>734000</v>
+        <v>181000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:33</t>
+          <t>2026-10-20 21:45:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.35%9920</t>
+          <t>-5.2%1185</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>9920</v>
+        <v>1185</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.00%92,000</t>
+          <t>2.91%734,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.91%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>92000</v>
+        <v>734000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:33</t>
+          <t>2026-10-20 21:45:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.22%882</t>
+          <t>-0.52%288</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>882</v>
+        <v>288</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.57%884,000</t>
+          <t>2.74%2,843,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.74%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>884000</v>
+        <v>2843000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:33</t>
+          <t>2026-10-20 21:45:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.31%1640</t>
+          <t>-2.13%1605</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-2.13%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1640</v>
+        <v>1605</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.56%475,000</t>
+          <t>2.55%475,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.55%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:33</t>
+          <t>2026-10-20 21:45:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+4.68%7830</t>
+          <t>-1.09%7745</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+4.68%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7830</v>
+        <v>7745</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.50%97,000</t>
+          <t>2.52%97,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:33</t>
+          <t>2026-10-20 21:45:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3044健鼎</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.2%577</t>
+          <t>-4.31%844</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-4.31%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>577</v>
+        <v>844</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.44%1,287,000</t>
+          <t>2.50%884,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1287000</v>
+        <v>884000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:36</t>
+          <t>2026-10-20 21:45:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6505台塑化</t>
+          <t>3044健鼎</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-5.31%116</t>
+          <t>-1.73%567</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>116</v>
+        <v>567</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.35%6,147,000</t>
+          <t>2.45%1,287,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>6147000</v>
+        <v>1287000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:36</t>
+          <t>2026-10-20 21:45:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+0.81%3715</t>
+          <t>-2.02%3640</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-2.02%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3715</v>
+        <v>3640</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.25%184,000</t>
+          <t>2.24%184,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:36</t>
+          <t>2026-10-20 21:45:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.13%131.5</t>
+          <t>-3.42%127</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>131.5</v>
+        <v>127</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.81%4,192,000</t>
+          <t>1.78%4,192,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:36</t>
+          <t>2026-10-20 21:45:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6278台表科</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-3.02%289.5</t>
+          <t>-1.75%1970</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.02%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>289.5</v>
+        <v>1970</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.74%1,830,000</t>
+          <t>1.66%252,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1830000</v>
+        <v>252000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:36</t>
+          <t>2026-10-20 21:45:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>2603長榮</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-1.86%158.5</t>
+          <t>-0.95%259.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>158.5</v>
+        <v>259.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.62%3,104,000</t>
+          <t>1.63%1,871,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>3104000</v>
+        <v>1871000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:36</t>
+          <t>2026-10-20 21:45:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.32%262</t>
+          <t>-3.15%153.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>-3.15%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>262</v>
+        <v>153.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.61%1,871,000</t>
+          <t>1.60%3,104,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1871000</v>
+        <v>3104000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:36</t>
+          <t>2026-10-20 21:45:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.27%73.4</t>
+          <t>-2.45%71.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>73.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.58%6,547,000</t>
+          <t>1.57%6,547,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:36</t>
+          <t>2026-10-20 21:45:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>6505台塑化</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.42%6245</t>
+          <t>-8.19%106.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-8.19%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6245</v>
+        <v>106.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.56%76,000</t>
+          <t>1.54%4,327,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>76000</v>
+        <v>4327000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:36</t>
+          <t>2026-10-20 21:45:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-3.03%15980</t>
+          <t>+0.97%207.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.03%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>15980</v>
+        <v>207.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.49%28,400</t>
+          <t>1.54%2,208,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>28400</v>
+        <v>2208000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:36</t>
+          <t>2026-10-20 21:45:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.14%205.5</t>
+          <t>-4.32%5975</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>-4.32%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>205.5</v>
+        <v>5975</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.49%2,208,000</t>
+          <t>1.52%76,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2208000</v>
+        <v>76000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:36</t>
+          <t>2026-10-20 21:45:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.99%1975</t>
+          <t>-0.5%15900</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1975</v>
+        <v>15900</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.48%228,000</t>
+          <t>1.51%28,400</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>228000</v>
+        <v>28400</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:36</t>
+          <t>2026-10-20 21:45:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+2.17%1885</t>
+          <t>-2.53%1925</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>-2.53%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1885</v>
+        <v>1925</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.37%221,000</t>
+          <t>1.47%228,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>221000</v>
+        <v>228000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:36</t>
+          <t>2026-10-20 21:45:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2%2695</t>
+          <t>+2.12%1925</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2695</v>
+        <v>1925</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.26%142,000</t>
+          <t>1.43%221,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>142000</v>
+        <v>221000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:36</t>
+          <t>2026-10-20 21:45:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-5.82%534</t>
+          <t>-1.48%2655</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.82%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>534</v>
+        <v>2655</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.24%708,000</t>
+          <t>1.26%142,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>708000</v>
+        <v>142000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:36</t>
+          <t>2026-10-20 21:45:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.35%1405</t>
+          <t>-2.06%523</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-2.06%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1405</v>
+        <v>523</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.15%249,000</t>
+          <t>1.24%708,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>249000</v>
+        <v>708000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:37</t>
+          <t>2026-10-20 21:45:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.15%670</t>
+          <t>-6.05%1320</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-6.05%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>670</v>
+        <v>1320</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.02%464,000</t>
+          <t>1.10%249,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>464000</v>
+        <v>249000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:37</t>
+          <t>2026-10-20 21:45:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.37%180</t>
+          <t>-1.49%660</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>180</v>
+        <v>660</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.96%1,614,000</t>
+          <t>1.03%464,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1614000</v>
+        <v>464000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:37</t>
+          <t>2026-10-20 21:45:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3533嘉澤</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.55%1815</t>
+          <t>+5%189</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>+5%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1815</v>
+        <v>189</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.91%152,000</t>
+          <t>1.02%1,614,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>152000</v>
+        <v>1614000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:37</t>
+          <t>2026-10-20 21:45:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>3533嘉澤</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0%248</t>
+          <t>-0.55%1805</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>248</v>
+        <v>1805</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.90%1,107,336</t>
+          <t>0.92%152,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1107336</v>
+        <v>152000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:37</t>
+          <t>2026-10-20 21:45:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6147頎邦</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.24%208</t>
+          <t>-1.81%243.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>208</v>
+        <v>243.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.88%1,293,000</t>
+          <t>0.90%1,107,336</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1293000</v>
+        <v>1107336</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:37</t>
+          <t>2026-10-20 21:45:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>6147頎邦</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-4.18%263.5</t>
+          <t>-2.64%202.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-4.18%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>263.5</v>
+        <v>202.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.87%999,000</t>
+          <t>0.88%1,293,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>999000</v>
+        <v>1293000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:37</t>
+          <t>2026-10-20 21:45:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,34 +2700,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.84%239.5</t>
+          <t>-1.52%259.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>-1.52%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>239.5</v>
+        <v>259.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.76%960,000</t>
+          <t>0.87%999,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>960000</v>
+        <v>999000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:37</t>
+          <t>2026-10-20 21:45:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>7750新代</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.55%1820</t>
+          <t>+0.84%241.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1820</v>
+        <v>241.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.73%122,000</t>
+          <t>0.78%960,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>122000</v>
+        <v>960000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:37</t>
+          <t>2026-10-20 21:45:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>7750新代</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.98%2570</t>
+          <t>+0.27%1825</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2570</v>
+        <v>1825</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.69%82,000</t>
+          <t>0.75%122,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>82000</v>
+        <v>122000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:37</t>
+          <t>2026-10-20 21:45:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+1.26%2005</t>
+          <t>-3.11%2490</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2005</v>
+        <v>2490</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.69%104,000</t>
+          <t>0.68%82,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>104000</v>
+        <v>82000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:37</t>
+          <t>2026-10-20 21:45:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.48%100</t>
+          <t>-0.9%99.1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:37</t>
+          <t>2026-10-20 21:45:11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.8%547</t>
+          <t>0%547</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.46%257,000</t>
+          <t>0.47%257,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:37</t>
+          <t>2026-10-20 21:45:11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.04%570</t>
+          <t>-1.58%561</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:37</t>
+          <t>2026-10-20 21:45:11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-6.26%989</t>
+          <t>-1.82%971</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-6.26%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>989</v>
+        <v>971</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:37</t>
+          <t>2026-10-20 21:45:11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.64%774</t>
+          <t>+1.16%783</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>774</v>
+        <v>783</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.34%133,000</t>
+          <t>0.35%133,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:38</t>
+          <t>2026-10-20 21:45:12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,25 +3254,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-4.69%162.5</t>
+          <t>-3.38%157</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-4.69%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>162.5</v>
+        <v>157</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.32%592,000</t>
+          <t>0.31%592,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:38</t>
+          <t>2026-10-20 21:45:12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-1.53%225.5</t>
+          <t>-2.88%219</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>225.5</v>
+        <v>219</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:38</t>
+          <t>2026-10-20 21:45:12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.08%366</t>
+          <t>+0.14%366.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.08%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>366</v>
+        <v>366.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.21%178,000</t>
+          <t>0.22%178,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:38</t>
+          <t>2026-10-20 21:45:12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>3374精材</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+1.04%438</t>
+          <t>-3.61%5205</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-3.61%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>438</v>
+        <v>5205</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.14%100,000</t>
+          <t>0.12%7,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>100000</v>
+        <v>7000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:38</t>
+          <t>2026-10-20 21:45:12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,34 +3493,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>1476儒鴻</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+2.18%5400</t>
+          <t>+1.4%325.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>5400</v>
+        <v>325.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.12%7,000</t>
+          <t>0.08%70,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>7000</v>
+        <v>70000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:38</t>
+          <t>2026-10-20 21:45:12</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,25 +3559,25 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-1.95%125.5</t>
+          <t>-0.4%125</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>125.5</v>
+        <v>125</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.07%180,000</t>
+          <t>0.08%180,000</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:38</t>
+          <t>2026-10-20 21:45:12</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3615,25 +3615,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1476儒鴻</t>
+          <t>1215卜蜂</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-2.58%321</t>
+          <t>-0.94%105.5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>321</v>
+        <v>105.5</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.07%70,000</t>
+          <t>0.07%200,000</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>70000</v>
+        <v>200000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3650,67 +3650,6 @@
         </is>
       </c>
       <c r="M53" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-10-20 00:30:38</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>1215卜蜂</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>-0.47%106.5</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-0.47%</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>106.5</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>0.07%200,000</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>0.07%</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>200000</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-20_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:08</t>
+          <t>2026-10-20 21:55:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:08</t>
+          <t>2026-10-20 21:55:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:08</t>
+          <t>2026-10-20 21:55:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:08</t>
+          <t>2026-10-20 21:55:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:08</t>
+          <t>2026-10-20 21:55:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:08</t>
+          <t>2026-10-20 21:55:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:08</t>
+          <t>2026-10-20 21:55:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:08</t>
+          <t>2026-10-20 21:55:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:08</t>
+          <t>2026-10-20 21:55:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:08</t>
+          <t>2026-10-20 21:55:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:08</t>
+          <t>2026-10-20 21:55:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:08</t>
+          <t>2026-10-20 21:55:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:08</t>
+          <t>2026-10-20 21:55:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:08</t>
+          <t>2026-10-20 21:55:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:08</t>
+          <t>2026-10-20 21:55:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:10</t>
+          <t>2026-10-20 21:55:09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:10</t>
+          <t>2026-10-20 21:55:09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:10</t>
+          <t>2026-10-20 21:55:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:10</t>
+          <t>2026-10-20 21:55:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:10</t>
+          <t>2026-10-20 21:55:09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:10</t>
+          <t>2026-10-20 21:55:09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:10</t>
+          <t>2026-10-20 21:55:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:10</t>
+          <t>2026-10-20 21:55:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:10</t>
+          <t>2026-10-20 21:55:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:10</t>
+          <t>2026-10-20 21:55:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:10</t>
+          <t>2026-10-20 21:55:09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:10</t>
+          <t>2026-10-20 21:55:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:10</t>
+          <t>2026-10-20 21:55:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:10</t>
+          <t>2026-10-20 21:55:09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:10</t>
+          <t>2026-10-20 21:55:09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:11</t>
+          <t>2026-10-20 21:55:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:11</t>
+          <t>2026-10-20 21:55:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:11</t>
+          <t>2026-10-20 21:55:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:11</t>
+          <t>2026-10-20 21:55:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:11</t>
+          <t>2026-10-20 21:55:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:11</t>
+          <t>2026-10-20 21:55:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:11</t>
+          <t>2026-10-20 21:55:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:11</t>
+          <t>2026-10-20 21:55:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:11</t>
+          <t>2026-10-20 21:55:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:11</t>
+          <t>2026-10-20 21:55:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:11</t>
+          <t>2026-10-20 21:55:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:11</t>
+          <t>2026-10-20 21:55:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:11</t>
+          <t>2026-10-20 21:55:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:11</t>
+          <t>2026-10-20 21:55:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:11</t>
+          <t>2026-10-20 21:55:10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:12</t>
+          <t>2026-10-20 21:55:11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:12</t>
+          <t>2026-10-20 21:55:11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:12</t>
+          <t>2026-10-20 21:55:11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:12</t>
+          <t>2026-10-20 21:55:11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:12</t>
+          <t>2026-10-20 21:55:11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:12</t>
+          <t>2026-10-20 21:55:11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:12</t>
+          <t>2026-10-20 21:55:11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">

--- a/etf_holdings/2026-10-20_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:08</t>
+          <t>2026-10-20 22:21:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:08</t>
+          <t>2026-10-20 22:21:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:08</t>
+          <t>2026-10-20 22:21:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:08</t>
+          <t>2026-10-20 22:21:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:08</t>
+          <t>2026-10-20 22:21:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:08</t>
+          <t>2026-10-20 22:21:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:08</t>
+          <t>2026-10-20 22:21:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:08</t>
+          <t>2026-10-20 22:21:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:08</t>
+          <t>2026-10-20 22:21:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:08</t>
+          <t>2026-10-20 22:21:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:08</t>
+          <t>2026-10-20 22:21:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:08</t>
+          <t>2026-10-20 22:21:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:08</t>
+          <t>2026-10-20 22:21:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:08</t>
+          <t>2026-10-20 22:21:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:08</t>
+          <t>2026-10-20 22:21:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:09</t>
+          <t>2026-10-20 22:21:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:09</t>
+          <t>2026-10-20 22:21:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:09</t>
+          <t>2026-10-20 22:21:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:09</t>
+          <t>2026-10-20 22:21:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:09</t>
+          <t>2026-10-20 22:21:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:09</t>
+          <t>2026-10-20 22:21:01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:09</t>
+          <t>2026-10-20 22:21:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:09</t>
+          <t>2026-10-20 22:21:01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:09</t>
+          <t>2026-10-20 22:21:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:09</t>
+          <t>2026-10-20 22:21:01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:09</t>
+          <t>2026-10-20 22:21:01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:09</t>
+          <t>2026-10-20 22:21:01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:09</t>
+          <t>2026-10-20 22:21:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:09</t>
+          <t>2026-10-20 22:21:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:09</t>
+          <t>2026-10-20 22:21:01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:10</t>
+          <t>2026-10-20 22:21:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:10</t>
+          <t>2026-10-20 22:21:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:10</t>
+          <t>2026-10-20 22:21:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:10</t>
+          <t>2026-10-20 22:21:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:10</t>
+          <t>2026-10-20 22:21:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:10</t>
+          <t>2026-10-20 22:21:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:10</t>
+          <t>2026-10-20 22:21:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:10</t>
+          <t>2026-10-20 22:21:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:10</t>
+          <t>2026-10-20 22:21:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:10</t>
+          <t>2026-10-20 22:21:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:10</t>
+          <t>2026-10-20 22:21:02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:10</t>
+          <t>2026-10-20 22:21:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:10</t>
+          <t>2026-10-20 22:21:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:10</t>
+          <t>2026-10-20 22:21:02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:10</t>
+          <t>2026-10-20 22:21:02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:11</t>
+          <t>2026-10-20 22:21:04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:11</t>
+          <t>2026-10-20 22:21:04</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:11</t>
+          <t>2026-10-20 22:21:04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:11</t>
+          <t>2026-10-20 22:21:04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:11</t>
+          <t>2026-10-20 22:21:04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:11</t>
+          <t>2026-10-20 22:21:04</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:11</t>
+          <t>2026-10-20 22:21:04</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
